--- a/dataset_t6_grouped/results2/G4/G4_T6321_W0022F0003T0006Z000C1N83_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T6321_W0022F0003T0006Z000C1N83_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>13.51343879105343</v>
+        <v>2.195933803546183</v>
       </c>
       <c r="D2" t="n">
-        <v>14.86769488477367</v>
+        <v>2.416000418775722</v>
       </c>
       <c r="E2" t="n">
-        <v>19.34608955675369</v>
+        <v>3.143739552972475</v>
       </c>
       <c r="F2" t="n">
-        <v>17.57727797590329</v>
+        <v>2.856307671084285</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>59.18680272809918</v>
+        <v>9.617855443316117</v>
       </c>
       <c r="D3" t="n">
-        <v>57.64609372828313</v>
+        <v>9.367490230846009</v>
       </c>
       <c r="E3" t="n">
-        <v>19.34608955675369</v>
+        <v>3.143739552972475</v>
       </c>
       <c r="F3" t="n">
-        <v>17.57727797590329</v>
+        <v>2.856307671084285</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>41.38509316918189</v>
+        <v>6.725077639992056</v>
       </c>
       <c r="D4" t="n">
-        <v>32.87390933036399</v>
+        <v>5.342010266184148</v>
       </c>
       <c r="E4" t="n">
-        <v>19.34608955675369</v>
+        <v>3.143739552972475</v>
       </c>
       <c r="F4" t="n">
-        <v>17.57727797590329</v>
+        <v>2.856307671084285</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>62.17124248173143</v>
+        <v>10.10282690328136</v>
       </c>
       <c r="D5" t="n">
-        <v>55.56506312476451</v>
+        <v>9.029322757774233</v>
       </c>
       <c r="E5" t="n">
-        <v>19.34608955675369</v>
+        <v>3.143739552972475</v>
       </c>
       <c r="F5" t="n">
-        <v>17.57727797590329</v>
+        <v>2.856307671084285</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
